--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104557_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104557_W11.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7588</v>
+        <v>6.624</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2769</v>
+        <v>6.9832</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5181</v>
+        <v>-0.3593</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4859</v>
+        <v>4.4673</v>
       </c>
       <c r="H2" t="n">
-        <v>3.609</v>
+        <v>3.5992</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8769</v>
+        <v>0.8681</v>
       </c>
       <c r="J2" t="n">
-        <v>6.612</v>
+        <v>6.5721</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3811</v>
+        <v>4.3609</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2309</v>
+        <v>2.2112</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1261</v>
+        <v>-2.1048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5734</v>
+        <v>0.4645</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6914</v>
+        <v>0.8179</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1532</v>
+        <v>2.1474</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1248</v>
+        <v>-1.121</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0066</v>
+        <v>3.9134</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2685</v>
+        <v>2.0838</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7382</v>
+        <v>1.8296</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2198</v>
+        <v>1.2284</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0304</v>
+        <v>-0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2502</v>
+        <v>1.2544</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3119</v>
+        <v>2.3002</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0921</v>
+        <v>-1.0719</v>
       </c>
       <c r="N3" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2547</v>
+        <v>0.6363</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0434</v>
+        <v>-0.2164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.8528</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9752</v>
+        <v>1.2338</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3715</v>
+        <v>2.3503</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6037</v>
+        <v>-1.1165</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2008</v>
+        <v>-1.1946</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5051</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6957</v>
+        <v>-0.5419</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9926</v>
+        <v>1.2274</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3956</v>
+        <v>0.4826</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5971</v>
+        <v>0.7447</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2082</v>
+        <v>-2.4219</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1096</v>
+        <v>-1.1353</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.2866</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>1.589</v>
+        <v>0.9152</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6472</v>
+        <v>-0.2349</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9418</v>
+        <v>1.1501</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0579</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.6658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5174</v>
+        <v>1.1721</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4839</v>
+        <v>-0.0034</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9666</v>
+        <v>1.1755</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2144</v>
+        <v>2.194</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6654</v>
+        <v>1.4968</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.549</v>
+        <v>0.6972</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2312</v>
+        <v>1.978</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4849</v>
+        <v>1.3822</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7463</v>
+        <v>0.5958</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4457</v>
+        <v>0.216</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1503</v>
+        <v>0.1146</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2954</v>
+        <v>0.1014</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2176</v>
+        <v>0.7991</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1179</v>
+        <v>0.2949</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3356</v>
+        <v>0.5043</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0605</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4632</v>
+        <v>0.7077</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0784</v>
+        <v>-1.3347</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5415</v>
+        <v>2.0425</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6386</v>
+        <v>-2.6348</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4934</v>
+        <v>0.4994</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.132</v>
+        <v>-3.1343</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7552</v>
+        <v>-0.7721</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8834</v>
+        <v>-1.8628</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6141</v>
+        <v>0.849</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2571</v>
+        <v>-0.4928</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8712</v>
+        <v>1.3418</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8998</v>
+        <v>0.9002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7391</v>
+        <v>0.7423999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3954</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.219</v>
+        <v>2.073</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6144</v>
+        <v>-2.6219</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2535</v>
+        <v>-0.2573</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0259</v>
+        <v>1.0254</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2795</v>
+        <v>-1.2827</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0041</v>
+        <v>0.9885</v>
       </c>
       <c r="K7" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2576</v>
+        <v>-1.2458</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3118</v>
+        <v>0.1637</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U7" t="n">
-        <v>0.082</v>
+        <v>0.0501</v>
       </c>
       <c r="V7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4446</v>
+        <v>-0.5507</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2021</v>
+        <v>-2.3791</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2425</v>
+        <v>1.8285</v>
       </c>
       <c r="G8" t="n">
-        <v>0.276</v>
+        <v>0.1971</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2785</v>
+        <v>-0.1174</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5545</v>
+        <v>0.3145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4568</v>
+        <v>0.2389</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2149</v>
+        <v>0.1272</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6717</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1808</v>
+        <v>-0.0417</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0636</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>0.2028</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2095</v>
+        <v>0.3205</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0858</v>
+        <v>-0.3417</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1237</v>
+        <v>0.6622</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7032</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2176</v>
+        <v>-1.1193</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7103</v>
+        <v>-0.9242</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4927</v>
+        <v>-0.1951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1982</v>
+        <v>0.2787</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.111</v>
+        <v>-0.2786</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3092</v>
+        <v>0.5572</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2536</v>
+        <v>0.4494</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1416</v>
+        <v>-0.2208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.6703</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0554</v>
+        <v>-0.1708</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1973</v>
+        <v>-0.113</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3478</v>
+        <v>0.5353</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>0.3807</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3478</v>
+        <v>0.1546</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-1.7057</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0408</v>
+        <v>-1.9284</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6227</v>
+        <v>-1.5376</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4181</v>
+        <v>-0.3908</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.809</v>
+        <v>-1.818</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4225</v>
+        <v>-1.4353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3865</v>
+        <v>-0.3827</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.306</v>
+        <v>-1.3329</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.154</v>
+        <v>-1.1763</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.503</v>
+        <v>-0.4851</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3145</v>
+        <v>0.4343</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0484</v>
+        <v>0.0717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3629</v>
+        <v>0.3627</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9285</v>
+        <v>-2.9302</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1493</v>
+        <v>-1.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7792</v>
+        <v>-1.6302</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4268</v>
+        <v>-3.4316</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2624</v>
+        <v>-1.2718</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1644</v>
+        <v>-2.1597</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0447</v>
+        <v>-1.0674</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.333</v>
+        <v>-0.3522</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3821</v>
+        <v>-2.3642</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5039</v>
+        <v>0.5133</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U11" t="n">
-        <v>0.274</v>
+        <v>0.3997</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5785</v>
+        <v>-0.5763</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6786</v>
+        <v>-3.6254</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6257</v>
+        <v>-0.8298</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0529</v>
+        <v>-2.7957</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1853</v>
+        <v>0.182</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3635</v>
+        <v>1.3696</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1782</v>
+        <v>-1.1876</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7091</v>
+        <v>0.6827</v>
       </c>
       <c r="K12" t="n">
-        <v>2.0261</v>
+        <v>2.0167</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8127</v>
+        <v>0.2334</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9739</v>
+        <v>-0.1467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1612</v>
+        <v>0.3801</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7077</v>
+        <v>-4.6348</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2254</v>
+        <v>-4.4868</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4823</v>
+        <v>-0.148</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5031</v>
+        <v>-4.5079</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3361</v>
+        <v>-2.3405</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1671</v>
+        <v>-2.1674</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8674</v>
+        <v>-2.8885</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4067</v>
+        <v>-1.4209</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6357</v>
+        <v>-1.6194</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2813</v>
+        <v>0.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2299</v>
+        <v>-0.0049</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0514</v>
+        <v>0.3648</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.692000000000002</v>
+        <v>-1.6867</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0059</v>
+        <v>0.694700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.698</v>
+        <v>-2.381400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.2794</v>
+        <v>-5.296700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8906</v>
+        <v>1.868000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.170199999999999</v>
+        <v>-7.164899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>8.598000000000001</v>
+        <v>8.376300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>8.118899999999998</v>
+        <v>7.9778</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4791999999999994</v>
+        <v>0.398600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.8776</v>
+        <v>-13.6731</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.2281</v>
+        <v>-6.109900000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.649299999999999</v>
+        <v>-7.563499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S14" t="n">
-        <v>6.1999</v>
+        <v>6.224600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8315000000000001</v>
+        <v>-0.8163000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>7.0318</v>
+        <v>7.0411</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4782</v>
+        <v>-1.476599999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.2521</v>
+        <v>10.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.7302</v>
+        <v>-11.6837</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1641</v>
+        <v>7.7787</v>
       </c>
       <c r="E15" t="n">
-        <v>10.6128</v>
+        <v>10.7816</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.4486</v>
+        <v>-3.0029</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5604</v>
+        <v>5.5383</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5009</v>
+        <v>1.4884</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0595</v>
+        <v>4.0498</v>
       </c>
       <c r="J15" t="n">
-        <v>6.572</v>
+        <v>6.5272</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8084</v>
+        <v>2.7816</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7636</v>
+        <v>3.7456</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0116</v>
+        <v>-0.989</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0353</v>
+        <v>-0.3937</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2005</v>
+        <v>0.2058</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>6.0097</v>
+        <v>5.9921</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.564</v>
+        <v>1.7227</v>
       </c>
       <c r="E16" t="n">
-        <v>0.399</v>
+        <v>0.502</v>
       </c>
       <c r="F16" t="n">
-        <v>1.165</v>
+        <v>1.2206</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9503</v>
+        <v>0.9573</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2409</v>
+        <v>1.2462</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2905</v>
+        <v>-0.2889</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5997</v>
+        <v>1.5871</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6494</v>
+        <v>-0.6298</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9742</v>
+        <v>-0.828</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.747</v>
+        <v>-0.6298</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2271</v>
+        <v>-0.1983</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6542</v>
+        <v>0.6844</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3885</v>
+        <v>0.553</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0427</v>
+        <v>0.1313</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2911</v>
+        <v>-0.8547</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0204</v>
+        <v>-0.7752</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3115</v>
+        <v>-0.0795</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0358</v>
+        <v>-0.1238</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1775</v>
+        <v>0.7337</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8583</v>
+        <v>-0.8576</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7447</v>
+        <v>-0.7309</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.198</v>
+        <v>-1.5089</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4532</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2459</v>
+        <v>-0.6399</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9557</v>
+        <v>-0.7901</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2016</v>
+        <v>0.1503</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>2.1789</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>3.9709</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7712</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4435</v>
+        <v>0.0641</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3881</v>
+        <v>-2.2947</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0554</v>
+        <v>2.3588</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8372000000000001</v>
+        <v>1.3121</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7705</v>
+        <v>-0.0065</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0667</v>
+        <v>1.3186</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0766</v>
+        <v>2.0286</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7579</v>
+        <v>1.1721</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8345</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7164</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5284</v>
+        <v>-1.1786</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7678</v>
+        <v>0.4622</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9046</v>
+        <v>-0.3586</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0253</v>
+        <v>-0.8389</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1207</v>
+        <v>0.4802</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1853</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9851</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7997</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3907</v>
+        <v>-0.0328</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3484</v>
+        <v>0.128</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7391</v>
+        <v>-0.1609</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3223</v>
+        <v>-0.9667</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1703</v>
+        <v>0.4393</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.152</v>
+        <v>-1.406</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3447</v>
+        <v>0.6078</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.7272</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9784</v>
+        <v>-0.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0224</v>
+        <v>-1.5745</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.2879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8264</v>
+        <v>-1.2866</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5789</v>
+        <v>-0.7003</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2571</v>
+        <v>-0.5206</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8359</v>
+        <v>-0.1797</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3856</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2836</v>
+        <v>-0.2038</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6257</v>
+        <v>-2.8498</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3421</v>
+        <v>2.6461</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9729</v>
+        <v>-0.3234</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4372</v>
+        <v>-0.1668</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.41</v>
+        <v>-0.1566</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6229</v>
+        <v>-0.3674</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7375</v>
+        <v>0.6238</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1147</v>
+        <v>-0.9912</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5957</v>
+        <v>0.044</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3003</v>
+        <v>-0.7906</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2954</v>
+        <v>0.8345</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3826</v>
+        <v>-0.0185</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0484</v>
+        <v>-0.7297</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3342</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>-0.387</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.214</v>
+        <v>-1.018</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1561</v>
+        <v>-1.1025</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0579</v>
+        <v>0.0844</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1406</v>
+        <v>3.1398</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3131</v>
+        <v>-2.3121</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4537</v>
+        <v>5.4519</v>
       </c>
       <c r="J21" t="n">
-        <v>4.6393</v>
+        <v>4.5994</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0674</v>
+        <v>-1.0901</v>
       </c>
       <c r="L21" t="n">
-        <v>5.7068</v>
+        <v>5.6896</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4987</v>
+        <v>-1.4596</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2457</v>
+        <v>-1.2219</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4738</v>
+        <v>-1.267</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5122</v>
+        <v>-1.3965</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0384</v>
+        <v>0.1295</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7424</v>
+        <v>-2.7317</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.651</v>
+        <v>-0.5423</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0914</v>
+        <v>-2.1894</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.886</v>
+        <v>-0.8791</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5888</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2958</v>
+        <v>-0.2902</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2034</v>
+        <v>0.1956</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0894</v>
+        <v>-1.0747</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4857</v>
+        <v>-0.4947</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0169</v>
+        <v>-0.1438</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8518</v>
+        <v>-4.5768</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7836</v>
+        <v>-2.794</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0683</v>
+        <v>-1.7828</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6444</v>
+        <v>-2.6269</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2051</v>
+        <v>-1.1926</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4393</v>
+        <v>-1.4343</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3742</v>
+        <v>-1.3814</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2702</v>
+        <v>-1.2455</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7687</v>
+        <v>-1.5237</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-1.185</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5861</v>
+        <v>-0.3388</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.691900000000001</v>
+        <v>1.6868</v>
       </c>
       <c r="E24" t="n">
-        <v>2.698000000000002</v>
+        <v>2.3813</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0061</v>
+        <v>-0.6947999999999996</v>
       </c>
       <c r="G24" t="n">
-        <v>5.279599999999999</v>
+        <v>5.2967</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="I24" t="n">
-        <v>7.1704</v>
+        <v>7.1648</v>
       </c>
       <c r="J24" t="n">
-        <v>13.8776</v>
+        <v>13.6731</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2282</v>
+        <v>6.109599999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>7.6493</v>
+        <v>7.563300000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.597899999999999</v>
+        <v>-8.3764</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.1189</v>
+        <v>-7.9777</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4791</v>
+        <v>-0.3986000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1341</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0125</v>
+        <v>17.0723</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.2001</v>
+        <v>-6.224399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.0317</v>
+        <v>-7.0411</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8318</v>
+        <v>0.8164000000000002</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4783</v>
+        <v>1.4763</v>
       </c>
       <c r="W24" t="n">
-        <v>11.7304</v>
+        <v>11.6835</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.252</v>
+        <v>-10.2073</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104557_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104557_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.121</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.6658</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7423999999999999</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5763</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.0316</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.6837</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104557_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.2073</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
